--- a/tools/importer/reports/import-why-firstnet.report.xlsx
+++ b/tools/importer/reports/import-why-firstnet.report.xlsx
@@ -64,13 +64,13 @@
     <t>why-firstnet.report.json</t>
   </si>
   <si>
-    <t>["hero","columns-icons","cards","cards","columns","columns","accordion","form-newsletter"]</t>
+    <t>["hero","columns-icons","cards","cards-insights","columns","columns","accordion","form-newsletter"]</t>
   </si>
   <si>
     <t>why-firstnet</t>
   </si>
   <si>
-    <t>2026-02-11T16:10:15.754Z</t>
+    <t>2026-02-11T17:07:24.507Z</t>
   </si>
   <si>
     <t>Why Choose FirstNet for First Responder Communication Systems</t>
